--- a/jogos_2025-02-11.xlsx
+++ b/jogos_2025-02-11.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,109 +901,109 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Yeni Malatyaspor</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="O4" t="n">
+        <v>5</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="X4" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>['40']</t>
+        </is>
+      </c>
+      <c r="AG4" t="n">
         <v>2</v>
       </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M4" t="n">
-        <v>12.08</v>
-      </c>
-      <c r="N4" t="n">
-        <v>22</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>['14', '49']</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG4" t="n">
-        <v>0</v>
-      </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45699.45833333334</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,25 +1159,25 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1185,83 +1185,83 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>5.1</v>
+        <v>2.75</v>
       </c>
       <c r="M6" t="n">
-        <v>3.4</v>
+        <v>2.68</v>
       </c>
       <c r="N6" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="O6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P6" t="n">
         <v>1.72</v>
       </c>
-      <c r="O6" t="n">
-        <v>5</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.05</v>
-      </c>
       <c r="Q6" t="n">
-        <v>2.35</v>
+        <v>3.8</v>
       </c>
       <c r="R6" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="T6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD6" t="n">
         <v>1.46</v>
       </c>
-      <c r="S6" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="T6" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="X6" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.66</v>
-      </c>
       <c r="AE6" t="inlineStr">
         <is>
+          <t>['90']</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>['40']</t>
-        </is>
-      </c>
       <c r="AG6" t="n">
-        <v>2</v>
+        <v>1.38</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.18</v>
+        <v>1.41</v>
       </c>
       <c r="AI6" t="n">
-        <v>2.87</v>
+        <v>2.15</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.57</v>
+        <v>2.25</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45699.45833333334</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,25 +1288,25 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
         <v>1</v>
       </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1314,83 +1314,83 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.75</v>
+        <v>2.82</v>
       </c>
       <c r="M7" t="n">
-        <v>2.68</v>
+        <v>2.99</v>
       </c>
       <c r="N7" t="n">
-        <v>2.87</v>
+        <v>2.62</v>
       </c>
       <c r="O7" t="n">
         <v>3.6</v>
       </c>
       <c r="P7" t="n">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="R7" t="n">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="S7" t="n">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="T7" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="U7" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="V7" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="W7" t="n">
-        <v>1.81</v>
+        <v>1.57</v>
       </c>
       <c r="X7" t="n">
-        <v>1.98</v>
+        <v>2.15</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.34</v>
+        <v>2.77</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.28</v>
+        <v>1.43</v>
       </c>
       <c r="AA7" t="n">
-        <v>7.1</v>
+        <v>5.45</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>['90']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['4']</t>
         </is>
       </c>
       <c r="AG7" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AH7" t="n">
         <v>1.38</v>
       </c>
-      <c r="AH7" t="n">
-        <v>1.41</v>
-      </c>
       <c r="AI7" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AJ7" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45699.45833333334</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,25 +1417,25 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Yeni Malatyaspor</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
         <v>1</v>
       </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1443,83 +1443,83 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.82</v>
+        <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>2.99</v>
+        <v>12.08</v>
       </c>
       <c r="N8" t="n">
-        <v>2.62</v>
+        <v>22</v>
       </c>
       <c r="O8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
+          <t>['14', '49']</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>['4']</t>
-        </is>
-      </c>
       <c r="AG8" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45699.45833333334</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,19 +1675,19 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -1701,83 +1701,83 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.83</v>
+        <v>1.27</v>
       </c>
       <c r="M10" t="n">
-        <v>3.34</v>
+        <v>5</v>
       </c>
       <c r="N10" t="n">
-        <v>2.42</v>
+        <v>12</v>
       </c>
       <c r="O10" t="n">
-        <v>3.3</v>
+        <v>1.69</v>
       </c>
       <c r="P10" t="n">
-        <v>2.1</v>
+        <v>2.44</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.85</v>
+        <v>10</v>
       </c>
       <c r="R10" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="S10" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="T10" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="U10" t="n">
         <v>1.41</v>
       </c>
       <c r="V10" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="W10" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="X10" t="n">
-        <v>3.48</v>
+        <v>3.25</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.91</v>
+        <v>1.79</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.08</v>
+        <v>3.35</v>
       </c>
       <c r="AB10" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>['56']</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AI10" t="n">
         <v>1.28</v>
       </c>
-      <c r="AC10" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>['62', '90+1']</t>
-        </is>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AJ10" t="n">
-        <v>1.85</v>
+        <v>4.75</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45699.58333333334</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,19 +1804,19 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1830,83 +1830,83 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.27</v>
+        <v>2.83</v>
       </c>
       <c r="M11" t="n">
-        <v>5</v>
+        <v>3.34</v>
       </c>
       <c r="N11" t="n">
-        <v>12</v>
+        <v>2.42</v>
       </c>
       <c r="O11" t="n">
-        <v>1.69</v>
+        <v>3.3</v>
       </c>
       <c r="P11" t="n">
-        <v>2.44</v>
+        <v>2.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>10</v>
+        <v>2.85</v>
       </c>
       <c r="R11" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S11" t="n">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="T11" t="n">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="U11" t="n">
         <v>1.41</v>
       </c>
       <c r="V11" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="W11" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="X11" t="n">
-        <v>3.25</v>
+        <v>3.48</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.79</v>
+        <v>1.91</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.35</v>
+        <v>3.08</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.43</v>
+        <v>2</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>['56']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['62', '90+1']</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.04</v>
+        <v>1.58</v>
       </c>
       <c r="AH11" t="n">
-        <v>3.35</v>
+        <v>1.39</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.28</v>
+        <v>2.1</v>
       </c>
       <c r="AJ11" t="n">
-        <v>4.75</v>
+        <v>1.85</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45699.58333333334</v>
@@ -2191,25 +2191,25 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -2217,22 +2217,22 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.34</v>
+        <v>1.99</v>
       </c>
       <c r="M14" t="n">
-        <v>3.38</v>
+        <v>3.47</v>
       </c>
       <c r="N14" t="n">
-        <v>2.88</v>
+        <v>3.57</v>
       </c>
       <c r="O14" t="n">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="P14" t="n">
         <v>2.05</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.75</v>
+        <v>4.33</v>
       </c>
       <c r="R14" t="n">
         <v>1.44</v>
@@ -2241,59 +2241,59 @@
         <v>2.63</v>
       </c>
       <c r="T14" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="U14" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="V14" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W14" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="X14" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.77</v>
+        <v>1.61</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.75</v>
+        <v>4.33</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>['9', '17']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>['22']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.66</v>
+        <v>1.78</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AJ14" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45699.69791666666</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Carlisle United</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,34 +2346,34 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.98</v>
+        <v>1.74</v>
       </c>
       <c r="M15" t="n">
-        <v>3.37</v>
+        <v>3.65</v>
       </c>
       <c r="N15" t="n">
-        <v>2.29</v>
+        <v>4.5</v>
       </c>
       <c r="O15" t="n">
-        <v>3.75</v>
+        <v>2.3</v>
       </c>
       <c r="P15" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.88</v>
+        <v>4.5</v>
       </c>
       <c r="R15" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U15" t="n">
         <v>1.4</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T15" t="n">
-        <v>3</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.36</v>
       </c>
       <c r="V15" t="n">
         <v>1.05</v>
@@ -2382,47 +2382,47 @@
         <v>1.3</v>
       </c>
       <c r="X15" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="AB15" t="n">
         <v>1.3</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AD15" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>['90+4']</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH15" t="n">
         <v>2</v>
       </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>['76']</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AI15" t="n">
-        <v>2.38</v>
+        <v>1.57</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.73</v>
+        <v>2.7</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45699.69791666666</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,22 +2449,22 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2475,28 +2475,28 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.77</v>
+        <v>1.99</v>
       </c>
       <c r="M16" t="n">
-        <v>3.27</v>
+        <v>3.35</v>
       </c>
       <c r="N16" t="n">
-        <v>2.48</v>
+        <v>3.72</v>
       </c>
       <c r="O16" t="n">
-        <v>2.95</v>
+        <v>2.7</v>
       </c>
       <c r="P16" t="n">
         <v>2.05</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="R16" t="n">
         <v>1.4</v>
       </c>
       <c r="S16" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="T16" t="n">
         <v>2.8</v>
@@ -2511,47 +2511,47 @@
         <v>1.3</v>
       </c>
       <c r="X16" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="AB16" t="n">
         <v>1.3</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AD16" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
+          <t>['6', '17', '32']</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AG16" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AJ16" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45699.69791666666</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,16 +2965,16 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -2991,31 +2991,31 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.74</v>
+        <v>2.09</v>
       </c>
       <c r="M20" t="n">
-        <v>3.65</v>
+        <v>3.47</v>
       </c>
       <c r="N20" t="n">
-        <v>4.5</v>
+        <v>3.28</v>
       </c>
       <c r="O20" t="n">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="P20" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="R20" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S20" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="T20" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="U20" t="n">
         <v>1.4</v>
@@ -3030,44 +3030,44 @@
         <v>3.45</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AA20" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="AB20" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG20" t="n">
         <v>1.3</v>
       </c>
-      <c r="AC20" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>['90+4']</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AH20" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AJ20" t="n">
-        <v>2.7</v>
+        <v>2.38</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45699.69791666666</v>
@@ -3094,109 +3094,109 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="M21" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="O21" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X21" t="n">
         <v>3</v>
       </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
+      <c r="Y21" t="n">
         <v>2</v>
       </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L21" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="M21" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="N21" t="n">
-        <v>3.47</v>
-      </c>
-      <c r="O21" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>5</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T21" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W21" t="n">
+      <c r="Z21" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>['10', '61']</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>['8']</t>
+        </is>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AH21" t="n">
         <v>1.48</v>
       </c>
-      <c r="X21" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>['41', '45+2', '56']</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AI21" t="n">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AJ21" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45699.69791666666</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,109 +3223,109 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="M22" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="N22" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="O22" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S22" t="n">
         <v>3</v>
       </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L22" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="M22" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="N22" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="O22" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="P22" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>2</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3.5</v>
-      </c>
       <c r="T22" t="n">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="U22" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="V22" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="W22" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="X22" t="n">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="Z22" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
+          <t>['20']</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>['20', '28', '35', '62']</t>
-        </is>
-      </c>
       <c r="AG22" t="n">
-        <v>2.7</v>
+        <v>1.18</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.1</v>
+        <v>2.05</v>
       </c>
       <c r="AI22" t="n">
-        <v>3.25</v>
+        <v>1.5</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.36</v>
+        <v>2.88</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45699.69791666666</v>
@@ -3352,22 +3352,22 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -3378,22 +3378,22 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.99</v>
+        <v>4.4</v>
       </c>
       <c r="M23" t="n">
-        <v>3.35</v>
+        <v>3.56</v>
       </c>
       <c r="N23" t="n">
-        <v>3.72</v>
+        <v>1.78</v>
       </c>
       <c r="O23" t="n">
-        <v>2.7</v>
+        <v>5</v>
       </c>
       <c r="P23" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.8</v>
+        <v>2.4</v>
       </c>
       <c r="R23" t="n">
         <v>1.4</v>
@@ -3402,19 +3402,19 @@
         <v>2.75</v>
       </c>
       <c r="T23" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="U23" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="V23" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="W23" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="X23" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="Y23" t="n">
         <v>1.98</v>
@@ -3423,38 +3423,38 @@
         <v>1.77</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>['6', '17', '32']</t>
+          <t>['90+1']</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['53']</t>
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.67</v>
+        <v>1.2</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.8</v>
+        <v>2.88</v>
       </c>
       <c r="AJ23" t="n">
-        <v>2.35</v>
+        <v>1.5</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45699.69791666666</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,83 +3507,83 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.99</v>
+        <v>2.77</v>
       </c>
       <c r="M24" t="n">
-        <v>3.47</v>
+        <v>3.27</v>
       </c>
       <c r="N24" t="n">
-        <v>3.57</v>
+        <v>2.48</v>
       </c>
       <c r="O24" t="n">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="P24" t="n">
         <v>2.05</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.33</v>
+        <v>3.4</v>
       </c>
       <c r="R24" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S24" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="T24" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="U24" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="V24" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="W24" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="X24" t="n">
-        <v>2.9</v>
+        <v>3.45</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="AA24" t="n">
-        <v>4.33</v>
+        <v>3.35</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AC24" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AI24" t="n">
         <v>1.91</v>
       </c>
-      <c r="AD24" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AJ24" t="n">
-        <v>2.6</v>
+        <v>2.15</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45699.69791666666</v>
@@ -3610,22 +3610,22 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -3636,83 +3636,83 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.72</v>
+        <v>2.14</v>
       </c>
       <c r="M25" t="n">
-        <v>3.59</v>
+        <v>3.18</v>
       </c>
       <c r="N25" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="O25" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>5</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X25" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA25" t="n">
         <v>4.75</v>
       </c>
-      <c r="O25" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="P25" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X25" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>3.75</v>
-      </c>
       <c r="AB25" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AD25" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>['41', '45+2', '56']</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH25" t="n">
         <v>1.8</v>
       </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>['49']</t>
-        </is>
-      </c>
-      <c r="AF25" t="inlineStr">
-        <is>
-          <t>['68']</t>
-        </is>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AI25" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AJ25" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45699.69791666666</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,25 +3868,25 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H27" t="n">
         <v>1</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -3894,43 +3894,43 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>4.4</v>
+        <v>2.34</v>
       </c>
       <c r="M27" t="n">
-        <v>3.56</v>
+        <v>3.38</v>
       </c>
       <c r="N27" t="n">
-        <v>1.78</v>
+        <v>2.88</v>
       </c>
       <c r="O27" t="n">
-        <v>5</v>
+        <v>3.1</v>
       </c>
       <c r="P27" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.4</v>
+        <v>3.75</v>
       </c>
       <c r="R27" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S27" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="T27" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="U27" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W27" t="n">
         <v>1.36</v>
       </c>
-      <c r="V27" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.33</v>
-      </c>
       <c r="X27" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="Y27" t="n">
         <v>1.98</v>
@@ -3939,38 +3939,38 @@
         <v>1.77</v>
       </c>
       <c r="AA27" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="AB27" t="n">
         <v>1.28</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>['90+1']</t>
+          <t>['9', '17']</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>['53']</t>
+          <t>['22']</t>
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>2</v>
+        <v>1.36</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.2</v>
+        <v>1.66</v>
       </c>
       <c r="AI27" t="n">
-        <v>2.88</v>
+        <v>1.8</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1.5</v>
+        <v>2.25</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45699.69791666666</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,19 +3997,19 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -4023,83 +4023,83 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.09</v>
+        <v>1.72</v>
       </c>
       <c r="M28" t="n">
-        <v>3.47</v>
+        <v>3.59</v>
       </c>
       <c r="N28" t="n">
-        <v>3.28</v>
+        <v>4.75</v>
       </c>
       <c r="O28" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X28" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>['49']</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>['68']</t>
+        </is>
+      </c>
+      <c r="AG28" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AJ28" t="n">
         <v>2.75</v>
-      </c>
-      <c r="P28" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X28" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>2.38</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45699.69791666666</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,25 +4126,25 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -4152,83 +4152,83 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.65</v>
+        <v>5.9</v>
       </c>
       <c r="M29" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="N29" t="n">
-        <v>4.75</v>
+        <v>1.49</v>
       </c>
       <c r="O29" t="n">
-        <v>2.75</v>
+        <v>5.5</v>
       </c>
       <c r="P29" t="n">
-        <v>1.95</v>
+        <v>2.5</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.33</v>
+        <v>2</v>
       </c>
       <c r="R29" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U29" t="n">
         <v>1.53</v>
       </c>
-      <c r="S29" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T29" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.29</v>
-      </c>
       <c r="V29" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W29" t="n">
-        <v>1.39</v>
+        <v>1.24</v>
       </c>
       <c r="X29" t="n">
-        <v>2.59</v>
+        <v>4.2</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AA29" t="n">
-        <v>4.15</v>
+        <v>2.9</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.16</v>
+        <v>1.42</v>
       </c>
       <c r="AC29" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD29" t="n">
         <v>2.1</v>
       </c>
-      <c r="AD29" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>['59']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['20', '28', '35', '62']</t>
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.23</v>
+        <v>2.7</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.72</v>
+        <v>1.1</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.67</v>
+        <v>3.25</v>
       </c>
       <c r="AJ29" t="n">
-        <v>2.63</v>
+        <v>1.36</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45699.69791666666</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4270,7 +4270,7 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -4281,65 +4281,65 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="M30" t="n">
-        <v>3.59</v>
+        <v>3.6</v>
       </c>
       <c r="N30" t="n">
         <v>4.75</v>
       </c>
       <c r="O30" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S30" t="n">
         <v>2.38</v>
       </c>
-      <c r="P30" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S30" t="n">
-        <v>3</v>
-      </c>
       <c r="T30" t="n">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="U30" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="V30" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="W30" t="n">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
       <c r="X30" t="n">
-        <v>3.65</v>
+        <v>2.59</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.92</v>
+        <v>1.7</v>
       </c>
       <c r="AA30" t="n">
-        <v>3.1</v>
+        <v>4.15</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.35</v>
+        <v>1.16</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.91</v>
+        <v>1.67</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>['20']</t>
+          <t>['59']</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
@@ -4348,16 +4348,16 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AH30" t="n">
-        <v>2.05</v>
+        <v>1.72</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AJ30" t="n">
-        <v>2.88</v>
+        <v>2.63</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45699.69791666666</v>
@@ -4384,109 +4384,109 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Carlisle United</t>
         </is>
       </c>
       <c r="G31" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="M31" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="N31" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="O31" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X31" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD31" t="n">
         <v>2</v>
       </c>
-      <c r="H31" t="n">
-        <v>1</v>
-      </c>
-      <c r="I31" t="n">
-        <v>1</v>
-      </c>
-      <c r="J31" t="n">
-        <v>1</v>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L31" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="M31" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N31" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="O31" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P31" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T31" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W31" t="n">
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>['76']</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG31" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AH31" t="n">
         <v>1.38</v>
       </c>
-      <c r="X31" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z31" t="n">
+      <c r="AI31" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AJ31" t="n">
         <v>1.73</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE31" t="inlineStr">
-        <is>
-          <t>['10', '61']</t>
-        </is>
-      </c>
-      <c r="AF31" t="inlineStr">
-        <is>
-          <t>['8']</t>
-        </is>
-      </c>
-      <c r="AG31" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>2.1</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45699.69791666666</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,22 +4513,22 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H32" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -4539,83 +4539,83 @@
         </is>
       </c>
       <c r="L32" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="M32" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="N32" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="O32" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="P32" t="n">
         <v>2.25</v>
       </c>
-      <c r="M32" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="N32" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="O32" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="P32" t="n">
-        <v>2.3</v>
-      </c>
       <c r="Q32" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="R32" t="n">
         <v>1.33</v>
       </c>
       <c r="S32" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="T32" t="n">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="U32" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="V32" t="n">
         <v>1.04</v>
       </c>
       <c r="W32" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="X32" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.6</v>
+        <v>1.82</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.2</v>
+        <v>1.92</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['28']</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>['60', '68', '82']</t>
+          <t>['56']</t>
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.63</v>
+        <v>2.15</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="AJ32" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45699.70833333334</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,25 +4642,25 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H33" t="n">
         <v>1</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -4668,34 +4668,34 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="M33" t="n">
-        <v>3.55</v>
+        <v>3.61</v>
       </c>
       <c r="N33" t="n">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="O33" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="P33" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="Q33" t="n">
         <v>4.5</v>
       </c>
       <c r="R33" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S33" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T33" t="n">
+        <v>3</v>
+      </c>
+      <c r="U33" t="n">
         <v>1.36</v>
-      </c>
-      <c r="S33" t="n">
-        <v>3</v>
-      </c>
-      <c r="T33" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.4</v>
       </c>
       <c r="V33" t="n">
         <v>1.06</v>
@@ -4704,47 +4704,47 @@
         <v>1.35</v>
       </c>
       <c r="X33" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.77</v>
+        <v>2.01</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.98</v>
+        <v>1.81</v>
       </c>
       <c r="AA33" t="n">
         <v>3.75</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AD33" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['34', '82']</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>['5']</t>
+          <t>['56']</t>
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AH33" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AJ33" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45699.70833333334</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,19 +4771,19 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I34" t="n">
         <v>1</v>
@@ -4797,83 +4797,83 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.94</v>
+        <v>2.37</v>
       </c>
       <c r="M34" t="n">
-        <v>3.73</v>
+        <v>3.8</v>
       </c>
       <c r="N34" t="n">
-        <v>3.47</v>
+        <v>2.85</v>
       </c>
       <c r="O34" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P34" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S34" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T34" t="n">
         <v>2.2</v>
       </c>
-      <c r="P34" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S34" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T34" t="n">
-        <v>2.45</v>
-      </c>
       <c r="U34" t="n">
-        <v>1.48</v>
+        <v>1.62</v>
       </c>
       <c r="V34" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="W34" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="X34" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.82</v>
+        <v>1.55</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.92</v>
+        <v>2.3</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="AB34" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>['19', '80']</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>['60', '86', '90+2']</t>
+        </is>
+      </c>
+      <c r="AG34" t="n">
         <v>1.42</v>
       </c>
-      <c r="AC34" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AE34" t="inlineStr">
-        <is>
-          <t>['28']</t>
-        </is>
-      </c>
-      <c r="AF34" t="inlineStr">
-        <is>
-          <t>['56']</t>
-        </is>
-      </c>
-      <c r="AG34" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AH34" t="n">
-        <v>2.15</v>
+        <v>1.58</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="AJ34" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45699.70833333334</v>
@@ -4900,22 +4900,22 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
         <v>3</v>
       </c>
       <c r="I35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4926,83 +4926,83 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="M35" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="N35" t="n">
-        <v>2.85</v>
+        <v>3.09</v>
       </c>
       <c r="O35" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="P35" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="R35" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="S35" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="T35" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="X35" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z35" t="n">
         <v>2.2</v>
       </c>
-      <c r="U35" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X35" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AA35" t="n">
-        <v>2.2</v>
+        <v>2.88</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>['19', '80']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>['60', '86', '90+2']</t>
+          <t>['60', '68', '82']</t>
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="AI35" t="n">
         <v>1.73</v>
       </c>
       <c r="AJ35" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45699.70833333334</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,60 +5029,60 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
         <v>1</v>
       </c>
       <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
         <v>1</v>
       </c>
-      <c r="J36" t="n">
-        <v>0</v>
-      </c>
       <c r="K36" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="M36" t="n">
-        <v>3.61</v>
+        <v>3.55</v>
       </c>
       <c r="N36" t="n">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="O36" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="P36" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="Q36" t="n">
         <v>4.5</v>
       </c>
       <c r="R36" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S36" t="n">
+        <v>3</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U36" t="n">
         <v>1.4</v>
-      </c>
-      <c r="S36" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T36" t="n">
-        <v>3</v>
-      </c>
-      <c r="U36" t="n">
-        <v>1.36</v>
       </c>
       <c r="V36" t="n">
         <v>1.06</v>
@@ -5091,47 +5091,47 @@
         <v>1.35</v>
       </c>
       <c r="X36" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="Y36" t="n">
-        <v>2.01</v>
+        <v>1.77</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.81</v>
+        <v>1.98</v>
       </c>
       <c r="AA36" t="n">
         <v>3.75</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>['34', '82']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>['56']</t>
+          <t>['5']</t>
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AI36" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AJ36" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="AK36" s="3" t="n">
         <v>45699.70833333334</v>
@@ -5287,16 +5287,16 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>Boca Juniors</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Banfield</t>
+          <t>Independiente Rivadavia</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -5313,83 +5313,83 @@
         </is>
       </c>
       <c r="L38" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M38" t="n">
+        <v>3</v>
+      </c>
+      <c r="N38" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O38" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="P38" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>6.69</v>
+      </c>
+      <c r="R38" t="n">
         <v>1.55</v>
       </c>
-      <c r="M38" t="n">
-        <v>3.73</v>
-      </c>
-      <c r="N38" t="n">
-        <v>6.12</v>
-      </c>
-      <c r="O38" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="P38" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1.44</v>
-      </c>
       <c r="S38" t="n">
-        <v>2.55</v>
+        <v>2.41</v>
       </c>
       <c r="T38" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X38" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>['51', '83']</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG38" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AJ38" t="n">
         <v>3.1</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V38" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="X38" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AE38" t="inlineStr">
-        <is>
-          <t>['78']</t>
-        </is>
-      </c>
-      <c r="AF38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG38" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>3.4</v>
       </c>
       <c r="AK38" s="3" t="n">
         <v>45699.83333333334</v>
@@ -5416,16 +5416,16 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Boca Juniors</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Independiente Rivadavia</t>
+          <t>Banfield</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -5442,65 +5442,65 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="M39" t="n">
-        <v>3</v>
+        <v>3.73</v>
       </c>
       <c r="N39" t="n">
-        <v>1.5</v>
+        <v>6.12</v>
       </c>
       <c r="O39" t="n">
-        <v>2.37</v>
+        <v>2.15</v>
       </c>
       <c r="P39" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q39" t="n">
-        <v>6.69</v>
+        <v>5.75</v>
       </c>
       <c r="R39" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S39" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X39" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD39" t="n">
         <v>1.55</v>
       </c>
-      <c r="S39" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="T39" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="V39" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X39" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>1.51</v>
-      </c>
       <c r="AE39" t="inlineStr">
         <is>
-          <t>['51', '83']</t>
+          <t>['78']</t>
         </is>
       </c>
       <c r="AF39" t="inlineStr">
@@ -5509,16 +5509,16 @@
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AH39" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AI39" t="n">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="AJ39" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="AK39" s="3" t="n">
         <v>45699.83333333334</v>
